--- a/templates/_masters/TAX-002-pl-single-property-BLANK.xlsx
+++ b/templates/_masters/TAX-002-pl-single-property-BLANK.xlsx
@@ -12,8 +12,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revenue Log" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Expense Log" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly P&amp;L" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule E Summary" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Depreciation" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule E Summary" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Start'!$A$1:$L$50</definedName>
@@ -21,8 +22,10 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Expense Log'!$1:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Monthly P&amp;L'!$1:$5</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Monthly P&amp;L'!$A$1:$N$32</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Schedule E Summary'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'Schedule E Summary'!$A$1:$B$46</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Depreciation'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Depreciation'!$A$1:$B$30</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Schedule E Summary'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'Schedule E Summary'!$A$1:$B$46</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -30,12 +33,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="166" formatCode="0.000%"/>
     <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="169" formatCode="0.000"/>
   </numFmts>
   <fonts count="37">
     <font>
@@ -228,17 +232,23 @@
       <sz val="11"/>
     </font>
     <font>
+      <name val="Georgia"/>
+      <b val="1"/>
+      <color rgb="0012304E"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="006B7280"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <b val="1"/>
       <i val="1"/>
       <color rgb="002B2B2B"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Georgia"/>
-      <b val="1"/>
-      <color rgb="0012304E"/>
-      <sz val="14"/>
     </font>
     <font>
       <name val="Georgia"/>
@@ -252,12 +262,6 @@
       <b val="1"/>
       <color rgb="0012304E"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="006B7280"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="9">
@@ -454,7 +458,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -596,22 +600,55 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="26" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="33" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="33" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="33" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="32" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="33" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="28" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="32" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="34" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="34" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="35" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -621,13 +658,10 @@
     <xf numFmtId="168" fontId="26" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="36" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="1" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -636,8 +670,8 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -34198,7 +34232,7 @@
         </is>
       </c>
       <c r="J2" s="29">
-        <f>HYPERLINK("#'Schedule E Summary'!A1", "NEXT →")</f>
+        <f>HYPERLINK("#'Depreciation'!A1", "NEXT →")</f>
         <v/>
       </c>
       <c r="K2" s="30" t="n"/>
@@ -35509,6 +35543,297 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C9A24B"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:L30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="8" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="11">
+        <f>HYPERLINK("#'Monthly P&amp;L'!A1", "← BACK")</f>
+        <v/>
+      </c>
+      <c r="B2" s="12" t="n"/>
+      <c r="C2" s="12" t="n"/>
+      <c r="D2" s="37" t="inlineStr">
+        <is>
+          <t>DEPRECIATION</t>
+        </is>
+      </c>
+      <c r="J2" s="29">
+        <f>HYPERLINK("#'Schedule E Summary'!A1", "NEXT →")</f>
+        <v/>
+      </c>
+      <c r="K2" s="30" t="n"/>
+      <c r="L2" s="30" t="n"/>
+    </row>
+    <row r="3" ht="6" customHeight="1">
+      <c r="A3" s="1" t="n"/>
+      <c r="B3" s="1" t="n"/>
+      <c r="C3" s="1" t="n"/>
+      <c r="D3" s="1" t="n"/>
+      <c r="E3" s="1" t="n"/>
+      <c r="F3" s="1" t="n"/>
+      <c r="G3" s="1" t="n"/>
+      <c r="H3" s="1" t="n"/>
+      <c r="I3" s="1" t="n"/>
+      <c r="J3" s="1" t="n"/>
+      <c r="K3" s="1" t="n"/>
+      <c r="L3" s="1" t="n"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="38" t="inlineStr">
+        <is>
+          <t>Straight-line, 27.5-yr residential rental, mid-month convention — auto-fills Schedule E Line 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="57" t="inlineStr">
+        <is>
+          <t>Straight-Line Depreciation Calculator (27.5-Year Residential Rental)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="58" t="inlineStr">
+        <is>
+          <t>Building only. For asset-by-asset (5/7/15-yr) depreciation see thestrledger.com/portfolio-master.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="39" t="inlineStr">
+        <is>
+          <t>Purchase price ($):</t>
+        </is>
+      </c>
+      <c r="B9" s="50">
+        <f>'Property Info'!B10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="39" t="inlineStr">
+        <is>
+          <t>Closing costs (capitalizable, $):</t>
+        </is>
+      </c>
+      <c r="B10" s="50">
+        <f>'Property Info'!B11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="59" t="inlineStr">
+        <is>
+          <t>Total cost basis ($):</t>
+        </is>
+      </c>
+      <c r="B11" s="51">
+        <f>B9+B10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="39" t="inlineStr">
+        <is>
+          <t>Land value (estimate, $):</t>
+        </is>
+      </c>
+      <c r="B12" s="42" t="n"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="59" t="inlineStr">
+        <is>
+          <t>Depreciable basis ($):</t>
+        </is>
+      </c>
+      <c r="B13" s="51">
+        <f>B11-B12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="39" t="inlineStr">
+        <is>
+          <t>In-service date:</t>
+        </is>
+      </c>
+      <c r="B14" s="60">
+        <f>'Property Info'!B15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="39" t="inlineStr">
+        <is>
+          <t>Tax year:</t>
+        </is>
+      </c>
+      <c r="B15" s="61">
+        <f>Settings!$B$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="39" t="inlineStr">
+        <is>
+          <t>Prior-year accumulated depreciation ($):</t>
+        </is>
+      </c>
+      <c r="B16" s="42" t="n"/>
+    </row>
+    <row r="17" ht="8" customHeight="1"/>
+    <row r="18" ht="8" customHeight="1"/>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="39" t="inlineStr">
+        <is>
+          <t>Annual full-year depreciation:</t>
+        </is>
+      </c>
+      <c r="B19" s="47">
+        <f>B13/27.5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="62" t="inlineStr">
+        <is>
+          <t>Year of in-service date:</t>
+        </is>
+      </c>
+      <c r="B20" s="63">
+        <f>YEAR(B14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="62" t="inlineStr">
+        <is>
+          <t>Months in service this tax year:</t>
+        </is>
+      </c>
+      <c r="B21" s="64">
+        <f>IF(B15=B20, 12.5-MONTH(B14), IF(B15&gt;B20, 12, 0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="62" t="inlineStr">
+        <is>
+          <t>Mid-month proration factor:</t>
+        </is>
+      </c>
+      <c r="B22" s="65">
+        <f>B21/12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="66" t="inlineStr">
+        <is>
+          <t>Current-year depreciation ($):</t>
+        </is>
+      </c>
+      <c r="B23" s="67">
+        <f>B19*B22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="62" t="inlineStr">
+        <is>
+          <t>Years already depreciated (info):</t>
+        </is>
+      </c>
+      <c r="B24" s="63">
+        <f>MAX(0, B15-B20-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="62" t="inlineStr">
+        <is>
+          <t>Implied prior accumulated ($, estimate):</t>
+        </is>
+      </c>
+      <c r="B25" s="68">
+        <f>IF(B15&gt;B20, B19*B24+B19*((12.5-MONTH(B14))/12), 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="59" t="inlineStr">
+        <is>
+          <t>Accumulated depreciation through current year ($):</t>
+        </is>
+      </c>
+      <c r="B26" s="69">
+        <f>B16+B23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="26" customHeight="1">
+      <c r="A28" s="44" t="inlineStr">
+        <is>
+          <t>If purchase price (B9) is blank, enter it on the Property Info tab — it auto-pulls.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="A29" s="44" t="inlineStr">
+        <is>
+          <t>Land value (B12) is your estimate of the LAND-only portion of purchase price. The IRS does not let you depreciate land. A common starting point is 15–20% of total purchase, but check your county tax assessor's land/improvement split for accuracy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="44" t="inlineStr">
+        <is>
+          <t>If this is not your first year of service, enter the prior accumulated depreciation in row 16 from your last Schedule E. Otherwise the calculator's 'Implied prior' (row 25) is a rough estimate, not authoritative.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="D2:I2"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A4:L4"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="1" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00F6EFE2"/>
@@ -35538,7 +35863,7 @@
     </row>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="11">
-        <f>HYPERLINK("#'Monthly P&amp;L'!A1", "← BACK")</f>
+        <f>HYPERLINK("#'Depreciation'!A1", "← BACK")</f>
         <v/>
       </c>
       <c r="B2" s="12" t="n"/>
@@ -35577,35 +35902,35 @@
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="57" t="inlineStr">
+      <c r="A5" s="70" t="inlineStr">
         <is>
           <t>Tax Year:</t>
         </is>
       </c>
-      <c r="B5" s="58">
+      <c r="B5" s="61">
         <f>Settings!$B$5</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="57" t="inlineStr">
+      <c r="A6" s="70" t="inlineStr">
         <is>
           <t>Property:</t>
         </is>
       </c>
-      <c r="B6" s="59">
+      <c r="B6" s="71">
         <f>'Property Info'!B5</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="8" customHeight="1"/>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="57" t="inlineStr">
+      <c r="A8" s="70" t="inlineStr">
         <is>
           <t>Line 3 — Rents received</t>
         </is>
       </c>
-      <c r="B8" s="60">
+      <c r="B8" s="72">
         <f>'Monthly P&amp;L'!N7</f>
         <v/>
       </c>
@@ -35807,11 +36132,11 @@
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="53" t="inlineStr">
         <is>
-          <t>Depreciation (Line 20) — see note</t>
+          <t>Depreciation (Line 20) — auto from Depreciation tab</t>
         </is>
       </c>
       <c r="B28" s="50">
-        <f>'Monthly P&amp;L'!N26</f>
+        <f>Depreciation!B23</f>
         <v/>
       </c>
     </row>
@@ -35829,94 +36154,94 @@
     </row>
     <row r="31" ht="8" customHeight="1"/>
     <row r="32" ht="26" customHeight="1">
-      <c r="A32" s="61" t="inlineStr">
+      <c r="A32" s="57" t="inlineStr">
         <is>
           <t>Line 26 — Income or (loss)</t>
         </is>
       </c>
-      <c r="B32" s="62">
+      <c r="B32" s="73">
         <f>B8+B9-B30</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="10" customHeight="1"/>
     <row r="34" ht="32" customHeight="1">
-      <c r="A34" s="63">
+      <c r="A34" s="74">
         <f>IF(Settings!$B$15="Schedule E (passive)","→ Schedule E (Form 1040), Line 26 — passive activity rules apply.",IF(Settings!$B$15="Schedule C (active)","→ Schedule C, Line 31 — SE tax (15.3%) applies on net earnings.","→ Schedule classification not set — see Settings."))</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="64" t="inlineStr">
+      <c r="A36" s="75" t="inlineStr">
         <is>
           <t>Audit-Defense Checks</t>
         </is>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="57" t="inlineStr">
+      <c r="A37" s="70" t="inlineStr">
         <is>
           <t>Avg stay (nights):</t>
         </is>
       </c>
-      <c r="B37" s="65">
+      <c r="B37" s="76">
         <f>IFERROR(SUM('Revenue Log'!H6:H1005)/COUNTA('Revenue Log'!A6:A1005),0)</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="28" customHeight="1">
-      <c r="A38" s="66">
+      <c r="A38" s="77">
         <f>IF(B37=0,"→ Add bookings to Revenue Log to compute eligibility.",IF(B37&lt;=7,"✓ Avg stay ≤7 nights — STR loophole eligible (IRC §469 escape).","⚠ Avg stay &gt;7 nights — passive activity rules apply; losses limited."))</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="57" t="inlineStr">
+      <c r="A39" s="70" t="inlineStr">
         <is>
           <t>14-day / 10% threshold:</t>
         </is>
       </c>
-      <c r="B39" s="58">
+      <c r="B39" s="61">
         <f>MAX(14, 'Property Info'!B16*0.1)</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="57" t="inlineStr">
+      <c r="A40" s="70" t="inlineStr">
         <is>
           <t>Personal use days YTD:</t>
         </is>
       </c>
-      <c r="B40" s="58">
+      <c r="B40" s="61">
         <f>'Property Info'!B17</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="36" customHeight="1">
-      <c r="A41" s="66">
+      <c r="A41" s="77">
         <f>IF(B40&lt;=B39,"✓ Personal use within safe harbor — full deductibility (Pub 527).","⚠ Personal use exceeds 14 days OR 10% of rental days — property is a \"residence\"; rental losses cannot offset other income, excess expenses carry forward.")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="57" t="inlineStr">
+      <c r="A42" s="70" t="inlineStr">
         <is>
           <t>QBI §199A safe harbor met (250+ hrs):</t>
         </is>
       </c>
-      <c r="B42" s="59">
+      <c r="B42" s="71">
         <f>'Settings'!$B$16</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="24" customHeight="1">
-      <c r="A43" s="67">
+      <c r="A43" s="78">
         <f>IF(B42="Yes","✓ Eligible for the 20% QBI deduction (§199A).",IF(B42="No","→ Not eligible — track service hours on Mileage Log + ops tools.","→ Set Settings!B19 once you know your service hours."))</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="28" customHeight="1">
-      <c r="A44" s="68" t="inlineStr">
+      <c r="A44" s="58" t="inlineStr">
         <is>
           <t>ℹ NIIT (3.8%) applies to passive rental income above $200K single / $250K MFJ AGI thresholds. Material participation removes this — see Mileage Log YTD Hours.</t>
         </is>
@@ -35940,7 +36265,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00F6EFE2"/>
@@ -36010,12 +36335,12 @@
           <t>Active tax year:</t>
         </is>
       </c>
-      <c r="B5" s="69" t="n">
+      <c r="B5" s="79" t="n">
         <v>2026</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="68" t="inlineStr">
+      <c r="A6" s="58" t="inlineStr">
         <is>
           <t>Bump this each January. Every monthly aggregate on the Monthly P&amp;L tab filters by this year — without it, dashboards return $0 when the system clock doesn't match logged dates.</t>
         </is>
@@ -36023,7 +36348,7 @@
     </row>
     <row r="7" ht="8" customHeight="1"/>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="64" t="inlineStr">
+      <c r="A8" s="75" t="inlineStr">
         <is>
           <t>Tax Classification</t>
         </is>
@@ -36042,7 +36367,7 @@
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="68" t="inlineStr">
+      <c r="A10" s="58" t="inlineStr">
         <is>
           <t>If 'Yes', residence-to-property trips are deductible business travel. If 'No', they're commuting (non-deductible). Documenting this election is on you, not the IRS.</t>
         </is>
@@ -36050,7 +36375,7 @@
     </row>
     <row r="11" ht="6" customHeight="1"/>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="70" t="inlineStr">
+      <c r="A12" s="80" t="inlineStr">
         <is>
           <t>⚠ Substantial-services trigger: if you provide cleaning DURING stays, meals, or concierge, IRS treats this as a hospitality business — Schedule C is required (15.3% SE tax applies).</t>
         </is>
@@ -36083,14 +36408,14 @@
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="64" t="inlineStr">
+      <c r="A17" s="75" t="inlineStr">
         <is>
           <t>Expense category list (Schedule E)</t>
         </is>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="71" t="inlineStr">
+      <c r="A18" s="81" t="inlineStr">
         <is>
           <t>(Source for the Expense Log dropdown — don't reorder)</t>
         </is>
@@ -36216,14 +36541,14 @@
       </c>
     </row>
     <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="64" t="inlineStr">
+      <c r="A37" s="75" t="inlineStr">
         <is>
           <t>Year-end Archive</t>
         </is>
       </c>
     </row>
     <row r="38" ht="28" customHeight="1">
-      <c r="A38" s="72" t="inlineStr">
+      <c r="A38" s="82" t="inlineStr">
         <is>
           <t>Each January, copy YTD totals into the row for the closing year, then bump 'Active tax year' above and clear the logs for the new year.</t>
         </is>
@@ -36252,7 +36577,7 @@
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="73" t="n">
+      <c r="A40" s="83" t="n">
         <v>2024</v>
       </c>
       <c r="B40" s="42" t="n"/>
@@ -36260,7 +36585,7 @@
       <c r="D40" s="42" t="n"/>
     </row>
     <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="73" t="n">
+      <c r="A41" s="83" t="n">
         <v>2025</v>
       </c>
       <c r="B41" s="42" t="n"/>
@@ -36268,7 +36593,7 @@
       <c r="D41" s="42" t="n"/>
     </row>
     <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="73" t="n">
+      <c r="A42" s="83" t="n">
         <v>2026</v>
       </c>
       <c r="B42" s="42" t="n"/>
@@ -36276,7 +36601,7 @@
       <c r="D42" s="42" t="n"/>
     </row>
     <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="73" t="n">
+      <c r="A43" s="83" t="n">
         <v>2027</v>
       </c>
       <c r="B43" s="42" t="n"/>
@@ -36284,7 +36609,7 @@
       <c r="D43" s="42" t="n"/>
     </row>
     <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="73" t="n">
+      <c r="A44" s="83" t="n">
         <v>2028</v>
       </c>
       <c r="B44" s="42" t="n"/>
@@ -36292,7 +36617,7 @@
       <c r="D44" s="42" t="n"/>
     </row>
     <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="73" t="n">
+      <c r="A45" s="83" t="n">
         <v>2029</v>
       </c>
       <c r="B45" s="42" t="n"/>
@@ -36300,7 +36625,7 @@
       <c r="D45" s="42" t="n"/>
     </row>
     <row r="46" ht="16" customHeight="1">
-      <c r="A46" s="73" t="n">
+      <c r="A46" s="83" t="n">
         <v>2030</v>
       </c>
       <c r="B46" s="42" t="n"/>
